--- a/public/assets/media/svg/files/products.xlsx
+++ b/public/assets/media/svg/files/products.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myBee\final\mybeeCompany\public\assets\media\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -68,9 +63,6 @@
     <t>Cost</t>
   </si>
   <si>
-    <t>Price</t>
-  </si>
-  <si>
     <t>Main_Unit</t>
   </si>
   <si>
@@ -83,22 +75,25 @@
     <t>فروج مشوي</t>
   </si>
   <si>
-    <t>Fried Chicken1</t>
-  </si>
-  <si>
     <t>وجبة</t>
   </si>
   <si>
     <t>Tax</t>
   </si>
   <si>
-    <t>وجبات سريعة</t>
-  </si>
-  <si>
-    <t>الضريبة الصفرية (0.0%)</t>
-  </si>
-  <si>
-    <t>مقلي1</t>
+    <t>ضريبة القيمة المضافة (15.0%)</t>
+  </si>
+  <si>
+    <t>سندويشات</t>
+  </si>
+  <si>
+    <t>سندويش</t>
+  </si>
+  <si>
+    <t>Fried Chicken11</t>
+  </si>
+  <si>
+    <t>Price_with_tax</t>
   </si>
 </sst>
 </file>
@@ -210,7 +205,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -262,7 +257,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -456,7 +451,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -491,10 +486,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -518,21 +513,21 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -541,10 +536,10 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -559,10 +554,10 @@
         <v>15</v>
       </c>
       <c r="O2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" t="s">
         <v>17</v>
-      </c>
-      <c r="P2" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
